--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.41.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: to these â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]Affidavi</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 8</t>
@@ -626,7 +630,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -659,20 +663,24 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) :: 3aof CODY 3. At the time when such SubpÅ“na shall be served.</t>
+          <t>L80: line starts with digit/letter garbage token | suspicious token(s): 3aof (letter/digit mix) :: 3aof CODY 3. At the time when such Subpœna shall be served.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr"/>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to these €</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
@@ -715,7 +723,7 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: er that the Subp Ã¦ na to appear to and</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr"/>
@@ -723,7 +731,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -746,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -760,11 +768,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: country within which the Subp Ã¦ ena is to be</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -807,11 +811,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: after service of the Subp Ã¦ na, within which</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -854,11 +854,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: time when such Subp Ã¦ na shall be served,</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -901,11 +897,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Defendant was duly served with the Subp Ã¦ ena,</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -954,7 +946,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: A</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -977,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -997,7 +989,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 8</t>
+          <t>L106: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1025,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1038,7 +1030,11 @@
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1059,7 +1055,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
